--- a/output/laminas_comunales/comunal_o_ocup_a_2021_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>37.5754127700933</v>
+        <v>57.1431058192769</v>
       </c>
     </row>
     <row r="3">
@@ -399,67 +399,67 @@
         </is>
       </c>
       <c r="C3">
-        <v>33.0845410628019</v>
+        <v>55.5846824720565</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="C4">
-        <v>32.669941198199</v>
+        <v>52.9494686618955</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.5719262755675</v>
+        <v>51.5952351201633</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="C6">
-        <v>32.2700148728552</v>
+        <v>51.552881925014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C7">
-        <v>32.225479321819</v>
+        <v>51.2193656895723</v>
       </c>
     </row>
     <row r="8">
@@ -474,67 +474,1162 @@
         </is>
       </c>
       <c r="C8">
-        <v>30.5027976225049</v>
+        <v>49.6566791510612</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="C9">
-        <v>29.0481680758391</v>
+        <v>49.5608899297424</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="C10">
-        <v>28.2360710854947</v>
+        <v>49.2871727557792</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C11">
-        <v>27.1836886545243</v>
+        <v>48.4346391420696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>43.5349377242981</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>43.2822992656929</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>42.6549114517306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>42.1935219352194</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>41.7383812572816</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>40.9880166299829</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>40.980532431495</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>40.4208542713568</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>40.2073890949045</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>40.0958528951487</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>39.6002627855266</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>14203</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Lago Ranco</t>
         </is>
       </c>
-      <c r="C12">
+      <c r="C23">
+        <v>39.5893836721523</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>39.5707777299469</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>39.5669291338583</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>38.7482742751956</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>38.0769588684162</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>37.6689726463104</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>37.5754127700933</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>36.9377916025713</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>36.8836350643163</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>36.1951410658307</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>35.8933454876937</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>35.4950647748304</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>35.1212610601642</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>34.4199424736337</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>34.1136402828074</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>33.6665701429011</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>33.0845410628019</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>32.7390326209224</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>32.6703068122725</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>32.669941198199</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>32.5719262755675</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>32.4726590306089</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>32.2700148728552</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>32.225479321819</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>32.0136405412538</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>31.7323302191312</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>31.4094080846968</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>31.3918485793486</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>31.0734463276836</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>30.5027976225049</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>30.3135163754633</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>30.1907719609583</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>30.1454385191714</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>29.0481680758391</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>28.2360710854947</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>27.9579148732664</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>27.8106384763822</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>27.5444664031621</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>27.1836886545243</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>26.0831426392067</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>25.9073515198138</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>25.2075330065792</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C65">
         <v>24.8179679623614</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>24.8037273461002</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>24.4293919812568</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>23.8807163415414</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>23.3980714646759</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>23.0099662778959</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>22.1706887883358</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>22.0283926852743</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>19.336954062005</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>9.759000983042521</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>9.39995436915355</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>9.17547212230216</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>8.936</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>8.86849629781684</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>8.013830532212889</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>7.54209119156008</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>7.44779582366589</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>7.35767451217059</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>6.97868600307625</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>6.66111573688593</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>5.96870239579006</v>
       </c>
     </row>
   </sheetData>
